--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260623_212532.xlsx
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
